--- a/Class XI C, 2026-27.xlsx
+++ b/Class XI C, 2026-27.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\PycharmProjects\WelcomeScreen\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="716" uniqueCount="435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="717" uniqueCount="435">
   <si>
     <t>ROLL. NO</t>
   </si>
@@ -1336,7 +1336,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -1839,7 +1839,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:W94"/>
-  <sheetFormatPr defaultColWidth="14" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="14" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="3.54296875" style="1" customWidth="1"/>
     <col min="2" max="2" width="3" style="1" customWidth="1"/>
@@ -1867,7 +1867,7 @@
     <col min="24" max="16384" width="14" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:23" ht="14.25" customHeight="1">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -1938,7 +1938,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="2" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:23" ht="14.25" customHeight="1">
       <c r="A2" s="35">
         <v>1</v>
       </c>
@@ -2001,7 +2001,7 @@
       </c>
       <c r="W2" s="14"/>
     </row>
-    <row r="3" spans="1:23" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:23" s="2" customFormat="1" ht="14.25" customHeight="1">
       <c r="A3" s="34">
         <v>2</v>
       </c>
@@ -2054,7 +2054,7 @@
       </c>
       <c r="W3" s="14"/>
     </row>
-    <row r="4" spans="1:23" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:23" s="2" customFormat="1" ht="14.25" customHeight="1">
       <c r="A4" s="35">
         <v>3</v>
       </c>
@@ -2117,7 +2117,7 @@
       </c>
       <c r="W4" s="14"/>
     </row>
-    <row r="5" spans="1:23" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:23" s="2" customFormat="1" ht="14.25" customHeight="1">
       <c r="A5" s="34">
         <v>4</v>
       </c>
@@ -2180,7 +2180,7 @@
       </c>
       <c r="W5" s="14"/>
     </row>
-    <row r="6" spans="1:23" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:23" s="2" customFormat="1" ht="14.25" customHeight="1">
       <c r="A6" s="35">
         <v>5</v>
       </c>
@@ -2247,7 +2247,7 @@
       </c>
       <c r="W6" s="14"/>
     </row>
-    <row r="7" spans="1:23" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:23" s="2" customFormat="1" ht="14.25" customHeight="1">
       <c r="A7" s="34">
         <v>6</v>
       </c>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="W7" s="14"/>
     </row>
-    <row r="8" spans="1:23" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:23" s="2" customFormat="1" ht="14.25" customHeight="1">
       <c r="A8" s="35">
         <v>7</v>
       </c>
@@ -2373,7 +2373,7 @@
       </c>
       <c r="W8" s="14"/>
     </row>
-    <row r="9" spans="1:23" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:23" s="2" customFormat="1" ht="14.25" customHeight="1">
       <c r="A9" s="34">
         <v>8</v>
       </c>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="W9" s="14"/>
     </row>
-    <row r="10" spans="1:23" s="2" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:23" s="2" customFormat="1" ht="14.5">
       <c r="A10" s="35">
         <v>9</v>
       </c>
@@ -2503,7 +2503,7 @@
       </c>
       <c r="W10" s="14"/>
     </row>
-    <row r="11" spans="1:23" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:23" s="2" customFormat="1" ht="14.25" customHeight="1">
       <c r="A11" s="34">
         <v>10</v>
       </c>
@@ -2566,7 +2566,7 @@
       </c>
       <c r="W11" s="14"/>
     </row>
-    <row r="12" spans="1:23" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:23" s="2" customFormat="1" ht="14.25" customHeight="1">
       <c r="A12" s="35">
         <v>11</v>
       </c>
@@ -2629,7 +2629,7 @@
       </c>
       <c r="W12" s="14"/>
     </row>
-    <row r="13" spans="1:23" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:23" s="2" customFormat="1" ht="14.25" customHeight="1">
       <c r="A13" s="34">
         <v>12</v>
       </c>
@@ -2688,7 +2688,7 @@
       </c>
       <c r="W13" s="14"/>
     </row>
-    <row r="14" spans="1:23" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:23" s="2" customFormat="1" ht="14.25" customHeight="1">
       <c r="A14" s="35">
         <v>13</v>
       </c>
@@ -2751,7 +2751,7 @@
       </c>
       <c r="W14" s="14"/>
     </row>
-    <row r="15" spans="1:23" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:23" s="2" customFormat="1" ht="14.25" customHeight="1">
       <c r="A15" s="34">
         <v>14</v>
       </c>
@@ -2814,7 +2814,7 @@
       </c>
       <c r="W15" s="14"/>
     </row>
-    <row r="16" spans="1:23" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:23" s="2" customFormat="1" ht="14.25" customHeight="1">
       <c r="A16" s="35">
         <v>15</v>
       </c>
@@ -2877,7 +2877,7 @@
       </c>
       <c r="W16" s="14"/>
     </row>
-    <row r="17" spans="1:23" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:23" s="2" customFormat="1" ht="14.25" customHeight="1">
       <c r="A17" s="34">
         <v>16</v>
       </c>
@@ -2938,7 +2938,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="18" spans="1:23" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:23" s="2" customFormat="1" ht="14.25" customHeight="1">
       <c r="A18" s="35">
         <v>17</v>
       </c>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="W18" s="14"/>
     </row>
-    <row r="19" spans="1:23" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:23" s="2" customFormat="1" ht="14.25" customHeight="1">
       <c r="A19" s="34">
         <v>18</v>
       </c>
@@ -3064,7 +3064,7 @@
       </c>
       <c r="W19" s="14"/>
     </row>
-    <row r="20" spans="1:23" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:23" s="2" customFormat="1" ht="14.25" customHeight="1">
       <c r="A20" s="35">
         <v>19</v>
       </c>
@@ -3125,7 +3125,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="21" spans="1:23" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:23" s="2" customFormat="1" ht="14.25" customHeight="1">
       <c r="A21" s="34">
         <v>20</v>
       </c>
@@ -3188,7 +3188,7 @@
       </c>
       <c r="W21" s="14"/>
     </row>
-    <row r="22" spans="1:23" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:23" s="2" customFormat="1" ht="14.25" customHeight="1">
       <c r="A22" s="35">
         <v>21</v>
       </c>
@@ -3251,7 +3251,7 @@
       </c>
       <c r="W22" s="14"/>
     </row>
-    <row r="23" spans="1:23" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:23" s="2" customFormat="1" ht="14.25" customHeight="1">
       <c r="A23" s="34">
         <v>22</v>
       </c>
@@ -3318,7 +3318,7 @@
       </c>
       <c r="W23" s="14"/>
     </row>
-    <row r="24" spans="1:23" s="2" customFormat="1" ht="15.4" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:23" s="2" customFormat="1" ht="15.4" customHeight="1">
       <c r="A24" s="35">
         <v>23</v>
       </c>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="W24" s="14"/>
     </row>
-    <row r="25" spans="1:23" s="2" customFormat="1" ht="16.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:23" s="2" customFormat="1" ht="16.75" customHeight="1">
       <c r="A25" s="34">
         <v>24</v>
       </c>
@@ -3444,7 +3444,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="26" spans="1:23" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:23" s="2" customFormat="1" ht="14.25" customHeight="1">
       <c r="A26" s="35">
         <v>25</v>
       </c>
@@ -3505,7 +3505,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="27" spans="1:23" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:23" s="2" customFormat="1" ht="14.25" customHeight="1">
       <c r="A27" s="34">
         <v>26</v>
       </c>
@@ -3568,7 +3568,7 @@
       </c>
       <c r="W27" s="14"/>
     </row>
-    <row r="28" spans="1:23" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:23" s="2" customFormat="1" ht="14.25" customHeight="1">
       <c r="A28" s="35">
         <v>27</v>
       </c>
@@ -3627,7 +3627,7 @@
       </c>
       <c r="W28" s="14"/>
     </row>
-    <row r="29" spans="1:23" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:23" s="2" customFormat="1" ht="14.25" customHeight="1">
       <c r="A29" s="34">
         <v>28</v>
       </c>
@@ -3690,7 +3690,7 @@
       </c>
       <c r="W29" s="14"/>
     </row>
-    <row r="30" spans="1:23" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:23" s="2" customFormat="1" ht="14.25" customHeight="1">
       <c r="A30" s="35">
         <v>29</v>
       </c>
@@ -3753,7 +3753,7 @@
       </c>
       <c r="W30" s="14"/>
     </row>
-    <row r="31" spans="1:23" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:23" s="2" customFormat="1" ht="14.25" customHeight="1">
       <c r="A31" s="34">
         <v>30</v>
       </c>
@@ -3816,7 +3816,7 @@
       </c>
       <c r="W31" s="14"/>
     </row>
-    <row r="32" spans="1:23" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:23" s="2" customFormat="1" ht="14.25" customHeight="1">
       <c r="A32" s="35">
         <v>31</v>
       </c>
@@ -3879,7 +3879,7 @@
       </c>
       <c r="W32" s="14"/>
     </row>
-    <row r="33" spans="1:23" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:23" s="2" customFormat="1" ht="14.25" customHeight="1">
       <c r="A33" s="34">
         <v>32</v>
       </c>
@@ -3930,7 +3930,7 @@
       <c r="V33" s="14"/>
       <c r="W33" s="14"/>
     </row>
-    <row r="34" spans="1:23" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:23" s="2" customFormat="1" ht="14.25" customHeight="1">
       <c r="A34" s="35">
         <v>33</v>
       </c>
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W34" s="14"/>
     </row>
-    <row r="35" spans="1:23" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:23" s="2" customFormat="1" ht="14.25" customHeight="1">
       <c r="A35" s="34">
         <v>34</v>
       </c>
@@ -4058,7 +4058,7 @@
       </c>
       <c r="W35" s="14"/>
     </row>
-    <row r="36" spans="1:23" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:23" s="2" customFormat="1" ht="14.25" customHeight="1">
       <c r="A36" s="35">
         <v>35</v>
       </c>
@@ -4117,7 +4117,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="37" spans="1:23" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:23" s="2" customFormat="1" ht="14.25" customHeight="1">
       <c r="A37" s="34">
         <v>36</v>
       </c>
@@ -4180,7 +4180,7 @@
       </c>
       <c r="W37" s="14"/>
     </row>
-    <row r="38" spans="1:23" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:23" s="2" customFormat="1" ht="14.25" customHeight="1">
       <c r="A38" s="35">
         <v>37</v>
       </c>
@@ -4205,7 +4205,9 @@
       <c r="H38" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="I38" s="14"/>
+      <c r="I38" s="14" t="s">
+        <v>113</v>
+      </c>
       <c r="J38" s="14" t="s">
         <v>21</v>
       </c>
@@ -4243,7 +4245,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="39" spans="1:23" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:23" s="2" customFormat="1" ht="14.25" customHeight="1">
       <c r="A39" s="34">
         <v>38</v>
       </c>
@@ -4306,7 +4308,7 @@
       </c>
       <c r="W39" s="14"/>
     </row>
-    <row r="40" spans="1:23" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:23" s="2" customFormat="1" ht="14.25" customHeight="1">
       <c r="A40" s="35">
         <v>39</v>
       </c>
@@ -4369,7 +4371,7 @@
       </c>
       <c r="W40" s="14"/>
     </row>
-    <row r="41" spans="1:23" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:23" s="2" customFormat="1" ht="14.25" customHeight="1">
       <c r="A41" s="34">
         <v>40</v>
       </c>
@@ -4432,7 +4434,7 @@
       </c>
       <c r="W41" s="14"/>
     </row>
-    <row r="42" spans="1:23" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:23" s="2" customFormat="1" ht="14.25" customHeight="1">
       <c r="A42" s="35">
         <v>41</v>
       </c>
@@ -4495,7 +4497,7 @@
       </c>
       <c r="W42" s="14"/>
     </row>
-    <row r="43" spans="1:23" s="3" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:23" s="3" customFormat="1" ht="14.25" customHeight="1">
       <c r="A43" s="34">
         <v>42</v>
       </c>
@@ -4558,7 +4560,7 @@
       </c>
       <c r="W43" s="14"/>
     </row>
-    <row r="44" spans="1:23" s="3" customFormat="1" ht="17.649999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:23" s="3" customFormat="1" ht="17.649999999999999" customHeight="1">
       <c r="A44" s="35">
         <v>43</v>
       </c>
@@ -4619,7 +4621,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="45" spans="1:23" s="3" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:23" s="3" customFormat="1" ht="14.25" customHeight="1">
       <c r="A45" s="34">
         <v>44</v>
       </c>
@@ -4686,7 +4688,7 @@
       </c>
       <c r="W45" s="14"/>
     </row>
-    <row r="46" spans="1:23" s="3" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:23" s="3" customFormat="1" ht="14.25" customHeight="1">
       <c r="A46" s="35">
         <v>45</v>
       </c>
@@ -4747,7 +4749,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="47" spans="1:23" s="4" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:23" s="4" customFormat="1" ht="14.5">
       <c r="A47" s="34">
         <v>46</v>
       </c>
@@ -4810,7 +4812,7 @@
       </c>
       <c r="W47" s="14"/>
     </row>
-    <row r="48" spans="1:23" s="3" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:23" s="3" customFormat="1" ht="14.25" customHeight="1">
       <c r="A48" s="35">
         <v>47</v>
       </c>
@@ -4871,7 +4873,7 @@
       </c>
       <c r="W48" s="14"/>
     </row>
-    <row r="49" spans="1:23" s="3" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:23" s="3" customFormat="1" ht="14.25" customHeight="1">
       <c r="A49" s="34">
         <v>48</v>
       </c>
@@ -4938,7 +4940,7 @@
       </c>
       <c r="W49" s="14"/>
     </row>
-    <row r="50" spans="1:23" s="3" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:23" s="3" customFormat="1" ht="14.25" customHeight="1">
       <c r="A50" s="35">
         <v>49</v>
       </c>
@@ -5003,7 +5005,7 @@
       </c>
       <c r="W50" s="14"/>
     </row>
-    <row r="51" spans="1:23" s="4" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:23" s="4" customFormat="1" ht="14.25" customHeight="1">
       <c r="A51" s="34">
         <v>50</v>
       </c>
@@ -5066,7 +5068,7 @@
       </c>
       <c r="W51" s="14"/>
     </row>
-    <row r="52" spans="1:23" s="3" customFormat="1" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:23" s="3" customFormat="1" ht="14.5">
       <c r="A52" s="35">
         <v>51</v>
       </c>
@@ -5129,7 +5131,7 @@
       </c>
       <c r="W52" s="14"/>
     </row>
-    <row r="53" spans="1:23" s="5" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:23" s="5" customFormat="1" ht="14.25" customHeight="1">
       <c r="A53" s="34">
         <v>52</v>
       </c>
@@ -5192,7 +5194,7 @@
       </c>
       <c r="W53" s="14"/>
     </row>
-    <row r="54" spans="1:23" s="6" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:23" s="6" customFormat="1" ht="14.25" customHeight="1">
       <c r="A54" s="35">
         <v>53</v>
       </c>
@@ -5257,7 +5259,7 @@
       </c>
       <c r="W54" s="14"/>
     </row>
-    <row r="55" spans="1:23" s="7" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:23" s="7" customFormat="1" ht="14.25" customHeight="1">
       <c r="A55" s="34">
         <v>54</v>
       </c>
@@ -5324,45 +5326,45 @@
       </c>
       <c r="W55" s="14"/>
     </row>
-    <row r="56" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="57" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="58" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="59" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="60" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="61" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="62" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="63" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="64" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="65" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="66" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="67" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="68" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="69" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="70" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="71" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="72" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="73" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="74" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="75" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="76" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="77" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="78" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="79" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="80" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="81" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="82" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="83" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="84" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="85" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="86" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="87" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="88" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="89" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="90" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="91" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="92" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="93" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="94" ht="14.25" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="56" spans="1:23" ht="14.25" customHeight="1"/>
+    <row r="57" spans="1:23" ht="14.25" customHeight="1"/>
+    <row r="58" spans="1:23" ht="14.25" customHeight="1"/>
+    <row r="59" spans="1:23" ht="14.25" customHeight="1"/>
+    <row r="60" spans="1:23" ht="14.25" customHeight="1"/>
+    <row r="61" spans="1:23" ht="14.25" customHeight="1"/>
+    <row r="62" spans="1:23" ht="14.25" customHeight="1"/>
+    <row r="63" spans="1:23" ht="14.25" customHeight="1"/>
+    <row r="64" spans="1:23" ht="14.25" customHeight="1"/>
+    <row r="65" ht="14.25" customHeight="1"/>
+    <row r="66" ht="14.25" customHeight="1"/>
+    <row r="67" ht="14.25" customHeight="1"/>
+    <row r="68" ht="14.25" customHeight="1"/>
+    <row r="69" ht="14.25" customHeight="1"/>
+    <row r="70" ht="14.25" customHeight="1"/>
+    <row r="71" ht="14.25" customHeight="1"/>
+    <row r="72" ht="14.25" customHeight="1"/>
+    <row r="73" ht="14.25" customHeight="1"/>
+    <row r="74" ht="14.25" customHeight="1"/>
+    <row r="75" ht="14.25" customHeight="1"/>
+    <row r="76" ht="14.25" customHeight="1"/>
+    <row r="77" ht="14.25" customHeight="1"/>
+    <row r="78" ht="14.25" customHeight="1"/>
+    <row r="79" ht="14.25" customHeight="1"/>
+    <row r="80" ht="14.25" customHeight="1"/>
+    <row r="81" ht="14.25" customHeight="1"/>
+    <row r="82" ht="14.25" customHeight="1"/>
+    <row r="83" ht="14.25" customHeight="1"/>
+    <row r="84" ht="14.25" customHeight="1"/>
+    <row r="85" ht="14.25" customHeight="1"/>
+    <row r="86" ht="14.25" customHeight="1"/>
+    <row r="87" ht="14.25" customHeight="1"/>
+    <row r="88" ht="14.25" customHeight="1"/>
+    <row r="89" ht="14.25" customHeight="1"/>
+    <row r="90" ht="14.25" customHeight="1"/>
+    <row r="91" ht="14.25" customHeight="1"/>
+    <row r="92" ht="14.25" customHeight="1"/>
+    <row r="93" ht="14.25" customHeight="1"/>
+    <row r="94" ht="14.25" customHeight="1"/>
   </sheetData>
   <sortState ref="A2:W56">
     <sortCondition ref="E2:E56"/>
